--- a/05_Figures/F06_prediction/proteins/total/d_1rm_ext/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/total/d_1rm_ext/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -125,15 +125,15 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">NANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5PD</t>
+  </si>
+  <si>
     <t xml:space="preserve">CARS1</t>
   </si>
   <si>
-    <t xml:space="preserve">ATP5PD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NANS</t>
-  </si>
-  <si>
     <t xml:space="preserve">PSMA5</t>
   </si>
   <si>
@@ -143,6 +143,9 @@
     <t xml:space="preserve">EEF1B2</t>
   </si>
   <si>
+    <t xml:space="preserve">HSD17B12</t>
+  </si>
+  <si>
     <t xml:space="preserve">NPM1</t>
   </si>
   <si>
@@ -152,6 +155,9 @@
     <t xml:space="preserve">PSMD2</t>
   </si>
   <si>
+    <t xml:space="preserve">RASA4</t>
+  </si>
+  <si>
     <t xml:space="preserve">RPS17</t>
   </si>
   <si>
@@ -164,364 +170,379 @@
     <t xml:space="preserve">UBE2D3</t>
   </si>
   <si>
+    <t xml:space="preserve">CPT2</t>
+  </si>
+  <si>
     <t xml:space="preserve">GPD1L</t>
   </si>
   <si>
-    <t xml:space="preserve">HSD17B12</t>
+    <t xml:space="preserve">MPDU1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH7A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5MF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHORDC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERGIC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GYG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCMT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CKM</t>
   </si>
   <si>
     <t xml:space="preserve">MOCS2</t>
   </si>
   <si>
-    <t xml:space="preserve">PSMB5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RASA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACADM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPDU1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH7A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5MF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPN1</t>
+    <t xml:space="preserve">ROMO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INPP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANCL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS3A</t>
   </si>
   <si>
     <t xml:space="preserve">IBA57</t>
   </si>
   <si>
-    <t xml:space="preserve">PCMT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CKM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGIC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GYG1</t>
-  </si>
-  <si>
     <t xml:space="preserve">RCSD1</t>
   </si>
   <si>
-    <t xml:space="preserve">ROMO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLK</t>
+    <t xml:space="preserve">RPS5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP6V1B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPTIN11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARPC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPYSL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGST2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFAB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDCD6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMC6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RNF123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UQCC3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL6IP5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPNE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCUN1D1</t>
   </si>
   <si>
     <t xml:space="preserve">EHD4</t>
   </si>
   <si>
-    <t xml:space="preserve">INPP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP6V1B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHORDC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DPYSL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANCL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LSM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGST2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFAB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS16</t>
+    <t xml:space="preserve">FDXR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTARC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEK7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUDT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCYT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPLP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS15A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A16</t>
   </si>
   <si>
     <t xml:space="preserve">SH3BGR</t>
   </si>
   <si>
-    <t xml:space="preserve">UQCC3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARPC2</t>
+    <t xml:space="preserve">SMTNL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACOT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APPL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARMT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASPN</t>
   </si>
   <si>
     <t xml:space="preserve">ATP1A3</t>
   </si>
   <si>
+    <t xml:space="preserve">ATP2A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5PB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCDC43</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCT3</t>
   </si>
   <si>
-    <t xml:space="preserve">CPNE3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FDXR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GBE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTARC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEK7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUDT3</t>
+    <t xml:space="preserve">CD36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNDP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCTN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIABLO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIAPH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUSP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNLL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF1AX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPB41L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPM2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESYT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FITM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMPPB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNPDA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSDL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRPPRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRRC20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP3K20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFA9</t>
   </si>
   <si>
     <t xml:space="preserve">PCBP2</t>
   </si>
   <si>
-    <t xml:space="preserve">PCYT2</t>
+    <t xml:space="preserve">PDXK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN3</t>
   </si>
   <si>
     <t xml:space="preserve">PPP1R3A</t>
   </si>
   <si>
-    <t xml:space="preserve">PSMC6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPLP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS15A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEPTIN11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTNL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBCB</t>
+    <t xml:space="preserve">PPP2R2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMC5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PYGL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPLP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN4IP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMYD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPTAN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAGLN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THOP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMM50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG101</t>
   </si>
   <si>
     <t xml:space="preserve">UBA3</t>
   </si>
   <si>
-    <t xml:space="preserve">ABCB7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACOT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APPL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARL6IP5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARMT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5PB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAVIN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCDC43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLPP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNDP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCUN1D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIABLO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIAPH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUSP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNLL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF1AX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMPPB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNPDA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSDL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMPA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LRPPRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LRRC20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP3K20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDCD6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDXK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP2R2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMC5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PYGL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTN4IP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SORD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAT5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAGLN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THOP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIMM50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG101</t>
+    <t xml:space="preserve">UBE2B</t>
   </si>
   <si>
     <t xml:space="preserve">UBE2G1</t>
@@ -914,16 +935,16 @@
         <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.40172327912547</v>
+        <v>-0.441998593417799</v>
       </c>
       <c r="I2" t="n">
-        <v>0.151515726445575</v>
+        <v>0.157025389225414</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -947,29 +968,21 @@
         <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.40172327912547</v>
+        <v>-0.441998593417799</v>
       </c>
       <c r="I3" t="n">
-        <v>0.151515726445575</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.388059701492537</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.318407960199005</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.713971181076216</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.799808987489592</v>
-      </c>
+        <v>0.157025389225414</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -993,2206 +1006,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.228404890635649</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.263157960839744</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.943829033481388</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-1.11607644897466</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.251943707593825</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.400265988979048</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-2.36915721211242</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-2.26770521831129</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-1.03701517295752</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.766231108950766</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.748883248213619</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.0760570541028099</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-2.44970503778697</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.713020873413314</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.356129883268775</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.0973916112367864</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.146781037591245</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.743940950750019</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-1.87670691214669</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-1.35156212067465</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.0459761488030124</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.441192301500238</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.270672105924634</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.471112464184141</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-2.41627604023597</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.927147291152843</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.599980101751251</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-2.02034869872203</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.704353456153411</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.523938099816859</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.333297297986858</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.345828006357797</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-1.70604789780388</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-1.44973601619041</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.847747541963222</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.00442129283945181</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.810718497550972</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-1.81409581516081</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.45237421049619</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.409490652253456</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.0922455441195668</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.51812096993505</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-1.75827396857093</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-1.74229507522764</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-1.53233325738295</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.431260595695866</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.865720346117356</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.29005838946416</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.65578969936441</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-1.30785159348951</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.332327560537439</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.0478654657169881</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.122242559308042</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.722229014502754</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-4.89387093860345</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.778592058189009</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.803570155823157</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.263562256185559</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-1.03390020349519</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.137492575447144</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.314608832214426</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.433534327878576</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.411779673951814</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.191082518110446</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.943826718484003</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0.397262696431285</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-1.23665015677882</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.0850891756350053</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.145569793223031</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-1.26555168322059</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0.292696602958667</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-1.04994998386309</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.598507617721072</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.557721614392232</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.503999509355904</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-1.7061974575735</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.00123949995933947</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.375111548642784</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-1.41798409029593</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0.422605277003707</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.762083348351529</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.47175351562321</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-1.71730444038647</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.794418202503708</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.841885940057448</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-1.71783133036437</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-2.03121636722296</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.374642984757494</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-1.11039467138632</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0.024492265089451</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.74623341820352</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.249731742124447</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.12878367429115</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.635002376989993</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-1.12472365181436</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-0.868546999326768</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>0.650939956370814</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-2.32723962992086</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-2.28556375936011</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.294580286786607</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.369216697159125</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-1.83600812658946</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.653802905122192</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-1.26037242675057</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.83760130694871</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>0.238186034153327</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.311579070072351</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.107259885926664</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>0.238400599561969</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.854782515009822</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-3.05040817296088</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>0.169284571094494</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.218450969316806</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.15163672509931</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-1.26913342506803</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>0.439101816896755</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.536893135036046</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>0.188295426117498</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-2.44638233316212</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.713131590626666</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.547859771729539</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-0.550724005559914</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.470036147618039</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>0.380083117898369</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.478253792133131</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-1.08245513408495</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.809375657409553</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.629761362165701</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.996855352829485</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.276146784042504</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.878387272565722</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.0466007737872374</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-1.23974043156459</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-1.80443848782181</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.44432927995045</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>0.11241085185983</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-2.47428702069709</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-1.44090839687161</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.352082425119403</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.120096456235435</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.338956507280833</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-1.17694286008558</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.676837570827431</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.180980254349357</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-2.32335649801902</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>0.224538458617843</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.616378389137917</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.419628053125427</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>0.558388471795782</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.105698979094709</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.555542533510222</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>0.505549254677281</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-1.8357391076951</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.926170519746304</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-1.32148055359563</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-1.08134000795194</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.158303573987193</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.368280087015402</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-1.56948871648742</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.761187909613781</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.316332630612459</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>0.267666074050504</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.849414715214405</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.131129029961625</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.944824356886322</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-1.05746535985381</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>0.537671612894979</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.875184697477327</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.235503610093579</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.285057429034933</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-0.329768930859506</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-1.14892016510471</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>0.269788587867613</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-1.80764517282118</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-1.6426039453852</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.17575211262223</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>0.143050647665509</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.41584630446983</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.139215717152555</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.154355081986901</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-1.02355982727024</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.94530520804535</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-1.66746331235626</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-0.086488504660263</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>0.250543575731378</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.968056967871277</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.635976755829666</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-2.40499189787391</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>0.234685801950377</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-1.62613584593091</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-1.00081515490806</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-1.05884359030614</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-1.52801327900362</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.174545405151386</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.372356510808295</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.768590857415796</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-1.72582471101225</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-0.888248291628101</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>0.17919908685677</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.168348233111582</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3235,7 +1048,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>6.15295254579827</v>
+        <v>6.46908586529973</v>
       </c>
     </row>
     <row r="3">
@@ -3252,7 +1065,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>10.3195571602157</v>
+        <v>10.064657122148</v>
       </c>
     </row>
     <row r="4">
@@ -3269,7 +1082,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>8.09614450090202</v>
+        <v>8.72893608653747</v>
       </c>
     </row>
     <row r="5">
@@ -3286,7 +1099,7 @@
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>14.2967102944301</v>
+        <v>14.891990653837</v>
       </c>
     </row>
     <row r="6">
@@ -3303,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>14.0330372804284</v>
+        <v>13.8700291070183</v>
       </c>
     </row>
     <row r="7">
@@ -3320,7 +1133,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>10.0201982723858</v>
+        <v>9.86900693051859</v>
       </c>
     </row>
     <row r="8">
@@ -3337,7 +1150,7 @@
         <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>9.34910946091524</v>
+        <v>9.1971697151311</v>
       </c>
     </row>
     <row r="9">
@@ -3354,7 +1167,7 @@
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>3.40927435482154</v>
+        <v>2.6457646883401</v>
       </c>
     </row>
     <row r="10">
@@ -3371,7 +1184,7 @@
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>11.4536831299692</v>
+        <v>11.5423764445747</v>
       </c>
     </row>
     <row r="11">
@@ -3388,7 +1201,7 @@
         <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>9.65439775058074</v>
+        <v>8.91118837584456</v>
       </c>
     </row>
     <row r="12">
@@ -3405,7 +1218,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>3.90089498868937</v>
+        <v>3.80631805535079</v>
       </c>
     </row>
     <row r="13">
@@ -3422,7 +1235,7 @@
         <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>11.8296275072553</v>
+        <v>11.9735819170738</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +1252,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>18.5689616327849</v>
+        <v>18.2295168315173</v>
       </c>
     </row>
   </sheetData>
@@ -3702,10 +1515,10 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.769230769230769</v>
+        <v>0.846153846153846</v>
       </c>
     </row>
     <row r="16">
@@ -3719,10 +1532,10 @@
         <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.769230769230769</v>
+        <v>0.846153846153846</v>
       </c>
     </row>
     <row r="17">
@@ -3787,10 +1600,10 @@
         <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>0.692307692307692</v>
+        <v>0.769230769230769</v>
       </c>
     </row>
     <row r="21">
@@ -3838,10 +1651,10 @@
         <v>57</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>0.615384615384615</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="24">
@@ -3855,10 +1668,10 @@
         <v>58</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>0.615384615384615</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="25">
@@ -3872,10 +1685,10 @@
         <v>59</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>0.615384615384615</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="26">
@@ -3889,10 +1702,10 @@
         <v>60</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>0.615384615384615</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="27">
@@ -3906,10 +1719,10 @@
         <v>61</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>0.615384615384615</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="28">
@@ -3923,10 +1736,10 @@
         <v>62</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>0.615384615384615</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="29">
@@ -3940,10 +1753,10 @@
         <v>63</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>0.615384615384615</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="30">
@@ -3957,10 +1770,10 @@
         <v>64</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>0.538461538461538</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="31">
@@ -3974,10 +1787,10 @@
         <v>65</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>0.538461538461538</v>
+        <v>0.615384615384615</v>
       </c>
     </row>
     <row r="32">
@@ -3991,10 +1804,10 @@
         <v>66</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>0.538461538461538</v>
+        <v>0.615384615384615</v>
       </c>
     </row>
     <row r="33">
@@ -4008,10 +1821,10 @@
         <v>67</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>0.538461538461538</v>
+        <v>0.615384615384615</v>
       </c>
     </row>
     <row r="34">
@@ -4025,10 +1838,10 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>0.538461538461538</v>
+        <v>0.615384615384615</v>
       </c>
     </row>
     <row r="35">
@@ -4076,10 +1889,10 @@
         <v>71</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>0.461538461538462</v>
+        <v>0.538461538461538</v>
       </c>
     </row>
     <row r="38">
@@ -4110,10 +1923,10 @@
         <v>73</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>0.384615384615385</v>
+        <v>0.461538461538462</v>
       </c>
     </row>
     <row r="40">
@@ -4127,10 +1940,10 @@
         <v>74</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>0.384615384615385</v>
+        <v>0.461538461538462</v>
       </c>
     </row>
     <row r="41">
@@ -4178,10 +1991,10 @@
         <v>77</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>0.307692307692308</v>
+        <v>0.384615384615385</v>
       </c>
     </row>
     <row r="44">
@@ -4212,10 +2025,10 @@
         <v>79</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>0.230769230769231</v>
+        <v>0.307692307692308</v>
       </c>
     </row>
     <row r="46">
@@ -4331,10 +2144,10 @@
         <v>86</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>0.153846153846154</v>
+        <v>0.230769230769231</v>
       </c>
     </row>
     <row r="53">
@@ -4348,10 +2161,10 @@
         <v>87</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>0.153846153846154</v>
+        <v>0.230769230769231</v>
       </c>
     </row>
     <row r="54">
@@ -4365,10 +2178,10 @@
         <v>88</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>0.153846153846154</v>
+        <v>0.230769230769231</v>
       </c>
     </row>
     <row r="55">
@@ -4739,10 +2552,10 @@
         <v>110</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>0.153846153846154</v>
+        <v>0.0769230769230769</v>
       </c>
     </row>
     <row r="77">
@@ -5762,6 +3575,125 @@
         <v>1</v>
       </c>
       <c r="E136" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="s">
+        <v>171</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="s">
+        <v>172</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="s">
+        <v>173</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="s">
+        <v>174</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="s">
+        <v>175</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="s">
+        <v>176</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.0769230769230769</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="s">
+        <v>177</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="n">
         <v>0.0769230769230769</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/total/d_1rm_ext/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/total/d_1rm_ext/spls/c_data/results.xlsx
@@ -971,7 +971,7 @@
         <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.441998593417799</v>
@@ -979,10 +979,18 @@
       <c r="I3" t="n">
         <v>0.157025389225414</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.398009950248756</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.298507462686567</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.76571901247419</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.839707426732569</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1006,6 +1014,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0781318375644032</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.258108866833977</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.28453465707865</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.951600770776398</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.453098787455857</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.208336250450174</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-2.27011000355624</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-2.60503129612452</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.02945668975139</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.778557294607148</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.767428706822603</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.035864380303738</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-2.80761949236421</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.87074238083273</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.153139926754416</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.0457988749961236</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0122194676639197</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.980070344827934</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-1.9300825746414</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.2485562652506</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.190825727651452</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.432611084878525</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.420818964243343</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.437187702233806</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-2.11680893784262</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.841703162700108</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.895172947783703</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-2.09038361399499</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.687891152330589</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.515354202650648</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.296392011364241</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.472933959268313</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.59458099197742</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-1.54377389319273</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.603047598771362</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.234312954090941</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.900771848980398</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-1.71933980910845</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.369128165923831</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.443760537021169</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.305614413005198</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.730452437132342</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-1.825607804155</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-2.02980047836061</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.25781777128762</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.471906735517994</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.905062466973674</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.197613290222632</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.52361123851771</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-1.03611425695689</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.473816914081972</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.0620715748663119</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.196056130198746</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.603181883717543</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-4.50107835111342</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-2.77721840133298</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.534553158593144</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.246022036361445</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.80948587421565</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.147524573452544</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.186616911669289</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.544831571177059</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.421997215788616</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.0632671738185098</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-1.50652148569713</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.600661607594918</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.2284853656843</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.103057030310039</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.0696328004858497</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-1.24887912332438</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.265611241550718</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-1.31539669663859</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.313644374261194</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.478010465027315</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.515424367950472</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-1.67151328451437</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.0158396677092938</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.401219823857455</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-1.05607152299152</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.131247621169209</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.540571704776246</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.558640672888605</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-2.77143354761525</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.682417052129359</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.924743118102912</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-1.74757862996823</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-2.4528814734353</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.599318920165983</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.980114069879191</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.0951139791503639</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-1.22526454782865</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.176614992008635</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-1.14978448779341</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.73658135214684</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-1.02321187157334</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.753465500741406</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.735339438189807</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-1.93091660882389</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-2.03369976985984</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.347862254916428</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.577182067048789</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-2.38610671171446</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.649223006803058</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-1.49709897998454</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.536066618564439</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.04235942930764</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.520148305925999</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.18666361199451</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.153691022379683</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-1.25556384399219</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-3.46689576284476</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.0206174582870851</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.190644941656121</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.272504871281422</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-1.25601614157957</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.547950027724613</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.647012444663403</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.318772692614176</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-2.44933105840565</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.942900597740335</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.350335788772693</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.684300945619337</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.537278686695776</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.519742602657813</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.497143917342436</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-1.12845269663238</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-1.31634331722534</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.697023685916904</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.99587754716398</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.531107537305568</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.879992478867255</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.0226714587924672</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-1.1849245179432</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-1.57550493233577</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.707432276425981</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.132956212658728</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-2.76862182326534</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-1.31638695292718</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-1.22295851026042</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.417331660133121</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.330399099816736</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-1.06332738949575</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.652891703304394</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.178799802310746</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-2.53997168183255</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0.242505738868155</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.68833550779222</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.316687813865841</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0.591242167216758</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.224766308440481</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.491911900135666</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0.451808553196203</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-2.04408339890669</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.954334974319448</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-1.44262491366847</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-1.22102998292112</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.161507350426404</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.362924076607537</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-1.69672257085407</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.730176596215553</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.366643949995943</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.411153106541155</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.848380701501732</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.180749944476386</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-1.14116886240541</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1.37784603146084</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.505009459176863</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.681386485305621</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.262476342735199</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.239964977434083</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.266256991533459</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-1.01779755692581</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.275986880342786</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-2.08142903882775</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-2.01337438596059</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.158768265336137</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.145320703124013</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0.141055625889985</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.17451212556854</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.0218240791639848</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-1.02588064129658</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.953986843111709</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-1.78930662134279</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.0728087166353082</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.268351406379703</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.811702159245536</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.629887624963334</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-2.00941388381304</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.111486748234568</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-2.01803169726692</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.970908986813377</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-1.11971753241138</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-1.5299678299895</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.16338043566513</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.417264290591164</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.568805894916065</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-2.37705657137302</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-1.06281562323191</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.163264029063731</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.100608430425718</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
